--- a/1_cleaned_sales_data.csv.xlsx
+++ b/1_cleaned_sales_data.csv.xlsx
@@ -2,31 +2,32 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thandiswa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F90BD839-B2C1-4599-A881-2BD227DCE071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9877EA92-5720-4BEC-B9BE-70A2644D55B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{637515CB-0ED9-4DED-ACE1-30CD5718BD2B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{637515CB-0ED9-4DED-ACE1-30CD5718BD2B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sales by State " sheetId="2" r:id="rId1"/>
-    <sheet name="Sales by Payment" sheetId="3" r:id="rId2"/>
-    <sheet name="Sales by Month" sheetId="4" r:id="rId3"/>
-    <sheet name="Sales Dataset" sheetId="1" r:id="rId4"/>
+    <sheet name="Dashboard" sheetId="5" r:id="rId1"/>
+    <sheet name="Sales by State " sheetId="2" r:id="rId2"/>
+    <sheet name="Sales by Payment" sheetId="3" r:id="rId3"/>
+    <sheet name="Sales by Month" sheetId="4" r:id="rId4"/>
+    <sheet name="Sales Dataset" sheetId="1" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="7" r:id="rId5"/>
+    <pivotCache cacheId="7" r:id="rId6"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8390" uniqueCount="1408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8394" uniqueCount="1412">
   <si>
     <t>Order ID</t>
   </si>
@@ -4250,6 +4251,18 @@
   </si>
   <si>
     <t>Sum of Amount</t>
+  </si>
+  <si>
+    <t>TOTAL SALES:$6,197,624</t>
+  </si>
+  <si>
+    <t>TOP STATE:New York $1.3M</t>
+  </si>
+  <si>
+    <t>TOP PAYMENT:Debit Card 23%</t>
+  </si>
+  <si>
+    <t>TOTAL ORDER</t>
   </si>
 </sst>
 </file>
@@ -4259,7 +4272,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;R&quot;#,##0.00;[Red]\-&quot;R&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4390,6 +4403,22 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="4" tint="0.39997558519241921"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="4" tint="0.39997558519241921"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -4736,7 +4765,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4752,6 +4781,8 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -4825,10 +4856,2319 @@
   </mc:AlternateContent>
   <c:pivotSource>
     <c:name>[1_cleaned_sales_data.csv.xlsx]Sales by State !PivotTable1</c:name>
+    <c:fmtId val="4"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Sales</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> by State</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.37908871869376237"/>
+          <c:y val="5.3035805948610668E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:numFmt formatCode="[$$-409]#,##0.00" sourceLinked="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:sysClr val="window" lastClr="FFFFFF"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="25000"/>
+                  <a:lumOff val="75000"/>
+                </a:sysClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                <a:prstGeom prst="wedgeRectCallout">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+              </c15:spPr>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sales by State '!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="[$$-409]#,##0.00" sourceLinked="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:sysClr val="window" lastClr="FFFFFF"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="25000"/>
+                    <a:lumOff val="75000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <a:prstGeom prst="wedgeRectCallout">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                </c15:spPr>
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sales by State '!$A$4:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>New York</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Florida</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>California</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Texas</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Illinois</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Ohio</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sales by State '!$B$4:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1130048</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1091174</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1086436</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1011475</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>978738</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>884768</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8F1E-43EA-9C2C-9FD2FF081B25}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1395931152"/>
+        <c:axId val="1395915312"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1395931152"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1395915312"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1395915312"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1395931152"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[1_cleaned_sales_data.csv.xlsx]Sales by Payment!PivotTable2</c:name>
+    <c:fmtId val="9"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Sales by Payment</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:sysClr val="window" lastClr="FFFFFF"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="25000"/>
+                  <a:lumOff val="75000"/>
+                </a:sysClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                <a:prstGeom prst="wedgeRectCallout">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+              </c15:spPr>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:sysClr val="window" lastClr="FFFFFF"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="25000"/>
+                  <a:lumOff val="75000"/>
+                </a:sysClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                <a:prstGeom prst="wedgeRectCallout">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+              </c15:spPr>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:sysClr val="window" lastClr="FFFFFF"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="25000"/>
+                  <a:lumOff val="75000"/>
+                </a:sysClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                <a:prstGeom prst="wedgeRectCallout">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+              </c15:spPr>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="11"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="12"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sales by Payment'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-4952-49C9-B9F8-53EA34E0E8AC}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-4952-49C9-B9F8-53EA34E0E8AC}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-4952-49C9-B9F8-53EA34E0E8AC}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-4952-49C9-B9F8-53EA34E0E8AC}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-4952-49C9-B9F8-53EA34E0E8AC}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:solidFill>
+                <a:sysClr val="window" lastClr="FFFFFF"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="25000"/>
+                    <a:lumOff val="75000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <a:prstGeom prst="wedgeRectCallout">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                </c15:spPr>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sales by Payment'!$A$4:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Debit Card</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Credit Card</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>UPI</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>COD</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>EMI</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sales by Payment'!$B$4:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1395035</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1281044</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1250473</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1141790</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1114297</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-4952-49C9-B9F8-53EA34E0E8AC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="0"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[1_cleaned_sales_data.csv.xlsx]Sales by Month!PivotTable3</c:name>
+    <c:fmtId val="3"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Sales by Month</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sales by Month'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sales by Month'!$A$4:$A$65</c:f>
+              <c:strCache>
+                <c:ptCount val="61"/>
+                <c:pt idx="0">
+                  <c:v>2020/03/01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2020/04/01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2020/05/01</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2020/06/01</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2020/07/01</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2020/08/01</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2020/09/01</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2020/10/01</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2020/11/01</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2020/12/01</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2021/01/01</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2021/02/01</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2021/03/01</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2021/04/01</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2021/05/01</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2021/06/01</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2021/07/01</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2021/08/01</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2021/09/01</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2021/10/01</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2021/11/01</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2021/12/01</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2022/01/01</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2022/02/01</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2022/03/01</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2022/04/01</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2022/05/01</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2022/06/01</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2022/07/01</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2022/08/01</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2022/09/01</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2022/10/01</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2022/11/01</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2022/12/01</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2023/01/01</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2023/02/01</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2023/03/01</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2023/04/01</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2023/05/01</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2023/06/01</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2023/07/01</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2023/08/01</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2023/09/01</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2023/10/01</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2023/11/01</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2023/12/01</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2024/01/01</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2024/02/01</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2024/03/01</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2024/04/01</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2024/05/01</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>2024/06/01</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>2024/07/01</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>2024/08/01</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>2024/09/01</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>2024/10/01</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>2024/11/01</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>2024/12/01</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>2025/01/01</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>2025/02/01</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2025/03/01</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sales by Month'!$B$4:$B$65</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="61"/>
+                <c:pt idx="0">
+                  <c:v>22991</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>133385</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>113287</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46900</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>38556</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>91117</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>109434</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>110836</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>108170</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>84725</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>22187</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>89829</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>103198</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>82463</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>124149</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>96616</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>85611</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>79494</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>57426</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>156211</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>150979</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>133283</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>145619</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>106735</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>93795</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>110873</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>143713</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>146997</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>61745</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>198965</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>48619</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>155508</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>42793</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>204413</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>64321</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>60982</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>105849</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>103109</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>83300</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>97770</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>181554</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>74870</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>108133</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>126861</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>88896</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>134078</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>47645</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>108414</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>119216</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>138052</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>117494</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>140745</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>129944</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>73384</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>84624</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>83105</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>60976</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>98879</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>112906</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>84712</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>52198</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-42B9-4203-8D31-FBD10313E30E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1395959952"/>
+        <c:axId val="1395960432"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1395959952"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1395960432"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1395960432"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1395959952"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[1_cleaned_sales_data.csv.xlsx]Sales by State !PivotTable1</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Sales by State</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -5193,7 +7533,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-GB"/>
@@ -5660,7 +8000,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-GB"/>
@@ -6512,6 +8852,126 @@
 </file>
 
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -8089,7 +10549,1664 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>161923</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>104776</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EAB053C-DA9C-4F7D-96F1-B1568C90D241}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>76199</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF15B1D8-0FE3-42F6-9858-BA0148DD856C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>152401</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>342901</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>76199</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB4371D2-2628-4B98-8D2E-093229CF03DC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -8130,7 +12247,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -8171,7 +12288,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -25127,7 +29244,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{989AE59F-4F2A-4297-9522-CECFDC1A40FC}" name="PivotTable1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{989AE59F-4F2A-4297-9522-CECFDC1A40FC}" name="PivotTable1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
@@ -25304,8 +29421,17 @@
   <dataFields count="1">
     <dataField name="Sum of Amount" fld="1" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="1">
+  <chartFormats count="2">
     <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -25328,7 +29454,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F15FA8B7-1EA7-4838-97D3-F576732C9107}" name="PivotTable2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F15FA8B7-1EA7-4838-97D3-F576732C9107}" name="PivotTable2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
   <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
@@ -25501,7 +29627,7 @@
   <dataFields count="1">
     <dataField name="Sum of Amount" fld="1" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="8">
+  <chartFormats count="14">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -25574,6 +29700,75 @@
         </references>
       </pivotArea>
     </chartFormat>
+    <chartFormat chart="9" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="9">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="10">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="11">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="12">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -25588,7 +29783,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3B9D2A1E-7CBF-42D1-A38C-9C001C29341A}" name="PivotTable3" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3B9D2A1E-7CBF-42D1-A38C-9C001C29341A}" name="PivotTable3" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:B65" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
@@ -25910,8 +30105,26 @@
   <dataFields count="1">
     <dataField name="Sum of Amount" fld="1" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="1">
+  <chartFormats count="3">
     <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -26249,6 +30462,50 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22190C9A-489C-4939-8B8A-E9684DD98722}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B1" s="12"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B2" s="12"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B3" s="12"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B4" s="12">
+        <f>COUNTA('Sales Dataset'!A:A)-1</f>
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="21" x14ac:dyDescent="0.35">
+      <c r="A5" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBBD1B3D-8D28-4372-BD85-824AE1C28CA3}">
   <dimension ref="A3:B10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -26327,7 +30584,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDF4BBE9-8CA6-4331-B22B-5097687895CC}">
   <dimension ref="A3:B9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -26398,7 +30655,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5099D954-8A68-4A6D-ACED-AD05F54EAD99}">
   <dimension ref="A3:B65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -26917,7 +31174,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51576AFB-C395-434C-9C99-00A27FCC4781}">
   <dimension ref="A1:L1195"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
